--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.66 ± 0.09</t>
+          <t>0.64 ± 0.10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.46 ± 0.13</t>
+          <t>0.33 ± 0.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.25 ± 0.19</t>
+          <t>0.24 ± 0.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.95 ± 0.07</t>
+          <t>0.78 ± 0.34</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.72 ± 0.22</t>
+          <t>0.70 ± 0.21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.86 ± 0.15</t>
+          <t>0.92 ± 0.09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
